--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1274,127 +1274,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>78116071</v>
-      </c>
-      <c r="B7" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1331</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Fläcklungört</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pulmonaria officinalis</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Lorensborg, 300 m SO , Sk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>432684.3496136545</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6166138.389847741</v>
-      </c>
-      <c r="S7" t="n">
-        <v>50</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sjöbo</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lövestad</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>M-Sbo-0168</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2019-05-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2019-05-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -799,12 +799,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>103602</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432635.492792789</v>
+        <v>432635</v>
       </c>
       <c r="R3" t="n">
-        <v>6166087.782735204</v>
+        <v>6166088</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -869,19 +864,9 @@
           <t>1999-07-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106058</v>
+        <v>106063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106063</v>
+        <v>106071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106071</v>
+        <v>106081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>105081</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>106366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106081</v>
+        <v>106366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106366</v>
+        <v>106367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106369</v>
+        <v>106373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106373</v>
+        <v>106386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106386</v>
+        <v>106387</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106387</v>
+        <v>106390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106390</v>
+        <v>106404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106404</v>
+        <v>106442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106442</v>
+        <v>106456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106442</v>
+        <v>106456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106466</v>
+        <v>106597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106466</v>
+        <v>106597</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106597</v>
+        <v>106598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106597</v>
+        <v>106598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106598</v>
+        <v>106599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106598</v>
+        <v>106599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 22337-2024 artfynd.xlsx
+++ b/artfynd/A 22337-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>377604</v>
       </c>
       <c r="B2" t="n">
-        <v>106614</v>
+        <v>106680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>63630517</v>
       </c>
       <c r="B3" t="n">
-        <v>106614</v>
+        <v>106680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>78117103</v>
+        <v>81357810</v>
       </c>
       <c r="B4" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221423</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lorensborg, 300 m SO, Sk</t>
+          <t>Norra infarten till Nyvångsskog, Sk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432657.8160682697</v>
+        <v>432636</v>
       </c>
       <c r="R4" t="n">
-        <v>6166104.934979097</v>
+        <v>6165988</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +972,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-05-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,11 +988,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>lövskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1017,22 +997,21 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Charlotte Wigermo</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Bengt Sandkull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81357810</v>
+        <v>81357632</v>
       </c>
       <c r="B5" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>219880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432636.2147800264</v>
+        <v>432636</v>
       </c>
       <c r="R5" t="n">
-        <v>6165987.871526162</v>
+        <v>6165988</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1097,19 +1076,9 @@
           <t>2012-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,15 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81357632</v>
+        <v>78117103</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,37 +1120,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219880</v>
+        <v>221423</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra infarten till Nyvångsskog, Sk</t>
+          <t>Lorensborg, 300 m SO, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432636.2147800264</v>
+        <v>432658</v>
       </c>
       <c r="R6" t="n">
-        <v>6165987.871526162</v>
+        <v>6166105</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,22 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-08-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,6 +1190,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>lövskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1245,14 +1204,10 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bengt Sandkull</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
